--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>147</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="G2">
-        <v>403</v>
+        <v>175</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>407</v>
+        <v>172</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="E2">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D3">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E3">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="G3">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="H3">
         <v>426</v>
